--- a/utils/monday_sprint_sprint_2025-3.xlsx
+++ b/utils/monday_sprint_sprint_2025-3.xlsx
@@ -264,7 +264,7 @@
     <t>15/10/2024</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>24/03/2026</t>
   </si>
   <si>
     <t>Outubro</t>
@@ -5245,7 +5245,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>78</v>
@@ -5259,7 +5259,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>85</v>

--- a/utils/monday_sprint_sprint_2025-3.xlsx
+++ b/utils/monday_sprint_sprint_2025-3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="268">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>29276</t>
+    <t>8088935443</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,13 +87,13 @@
     <t>19/12/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>22/12/2024</t>
   </si>
   <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
+    <t>Não</t>
   </si>
   <si>
     <t>Semana 3</t>
@@ -102,7 +102,7 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>'''</t>
+    <t>8094693990</t>
   </si>
   <si>
     <t>PDI_RespostaNew – A sequência que apresentar laudo ‘Analisar’ ou ‘Retrabalho’ criar nova PDI.</t>
@@ -111,10 +111,13 @@
     <t>20/12/2024</t>
   </si>
   <si>
+    <t>14/01/2025</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>29686</t>
+    <t>8455013812</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -126,19 +129,19 @@
     <t>11/02/2025</t>
   </si>
   <si>
+    <t>10/02/2025</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>29314</t>
+    <t>8337249520</t>
   </si>
   <si>
     <t>Erro sistema PCP Usinagem ( Erro de comunicação)</t>
@@ -147,67 +150,118 @@
     <t>27/01/2025</t>
   </si>
   <si>
+    <t>09/02/2025</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
     <t>Janeiro</t>
   </si>
   <si>
-    <t>29254</t>
+    <t>8454398060</t>
   </si>
   <si>
     <t>Cotas minima e máxima podem ser negativas</t>
   </si>
   <si>
+    <t>8454402890</t>
+  </si>
+  <si>
     <t>Passar modelo das planilhas</t>
   </si>
   <si>
+    <t>8454405826</t>
+  </si>
+  <si>
     <t>Tela PDI_RespostaNew alterar texto "Desvio" para "liberar desvio"</t>
   </si>
   <si>
+    <t>8454409396</t>
+  </si>
+  <si>
     <t>Estrutura da planilha de cotas</t>
   </si>
   <si>
+    <t>8454415682</t>
+  </si>
+  <si>
     <t>Verificar PDI_RespostaNew mensagem ao selecionar "analisar", alterou para "aprovado"</t>
   </si>
   <si>
+    <t>8455097605</t>
+  </si>
+  <si>
     <t>•	Verificar parte visual após conversão</t>
   </si>
   <si>
+    <t>8455130047</t>
+  </si>
+  <si>
     <t>•	Elaborar login para jato Scarfa</t>
   </si>
   <si>
+    <t>8455147681</t>
+  </si>
+  <si>
     <t>•	Criar transação Turno(APON14)</t>
   </si>
   <si>
+    <t>8455308619</t>
+  </si>
+  <si>
     <t>•	Criar transação de apontamento(APON15)</t>
   </si>
   <si>
+    <t>8455316964</t>
+  </si>
+  <si>
     <t>•	Criar transação de paradas(APON16)</t>
   </si>
   <si>
+    <t>8455324845</t>
+  </si>
+  <si>
     <t>•	Elaborar rotina para abrir e fechar turno</t>
   </si>
   <si>
+    <t>8455333165</t>
+  </si>
+  <si>
     <t>•	Elaborar rotina para inserir apontamento e parada</t>
   </si>
   <si>
+    <t>8455340320</t>
+  </si>
+  <si>
     <t>•	Elaborar tela de apontamento geral</t>
   </si>
   <si>
+    <t>8455356520</t>
+  </si>
+  <si>
     <t>•	Elaborar tela de paradas</t>
   </si>
   <si>
+    <t>8455364291</t>
+  </si>
+  <si>
     <t>•	Elaborar tela de turno</t>
   </si>
   <si>
+    <t>8455390600</t>
+  </si>
+  <si>
     <t>•	Validar construção do sistema</t>
   </si>
   <si>
+    <t>8455402307</t>
+  </si>
+  <si>
     <t>•	Criar transação para cadastro e definição dos ciclos</t>
   </si>
   <si>
-    <t>9827</t>
+    <t>2444634668</t>
   </si>
   <si>
     <t>Novo Recurso</t>
@@ -225,7 +279,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>27180</t>
+    <t>8232435779</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -240,10 +294,13 @@
     <t>13/01/2025</t>
   </si>
   <si>
+    <t>05/02/2025</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
-    <t>29680</t>
+    <t>8327452815</t>
   </si>
   <si>
     <t>Qlik Sense - Custos Logísticos na Oferta</t>
@@ -252,43 +309,55 @@
     <t>26/01/2025</t>
   </si>
   <si>
-    <t>29679</t>
+    <t>03/02/2025</t>
+  </si>
+  <si>
+    <t>8327454614</t>
   </si>
   <si>
     <t>Valor de Venda EXW + Custo de Entrega</t>
   </si>
   <si>
-    <t>29677</t>
+    <t>8327457274</t>
   </si>
   <si>
     <t>Qlik Sense - Base do WMS e Etiqueta Amarela (Entrada e estoque)</t>
   </si>
   <si>
-    <t>29610</t>
+    <t>29/01/2025</t>
+  </si>
+  <si>
+    <t>8327477646</t>
   </si>
   <si>
     <t>Relatório QSENSE - Refugo</t>
   </si>
   <si>
-    <t>29602</t>
+    <t>28/01/2025</t>
+  </si>
+  <si>
+    <t>8327479481</t>
   </si>
   <si>
     <t>Filtro tela de apontamento de parada</t>
   </si>
   <si>
-    <t>29599</t>
+    <t>06/02/2025</t>
+  </si>
+  <si>
+    <t>8327481579</t>
   </si>
   <si>
     <t>Relatório de Contas a receber - Gerencial no SENSE</t>
   </si>
   <si>
-    <t>29051</t>
+    <t>8330697403</t>
   </si>
   <si>
     <t>ANÁLISES CRÍTICAS PARCIAIS</t>
   </si>
   <si>
-    <t>29477</t>
+    <t>8327522457</t>
   </si>
   <si>
     <t>Qlik Sense - Custos de Exportação "ID"</t>
@@ -297,6 +366,9 @@
     <t>28392</t>
   </si>
   <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -318,49 +390,82 @@
     <t>Notas de consignado - Medição NIMBI - Geração de OC (WEB)</t>
   </si>
   <si>
+    <t>8331075747</t>
+  </si>
+  <si>
     <t>Refazer rateio do tempo de inspeção</t>
   </si>
   <si>
+    <t>8331092991</t>
+  </si>
+  <si>
     <t>Rateio de tempos e paradas Usinagem</t>
   </si>
   <si>
-    <t>27921</t>
+    <t>8337249199</t>
   </si>
   <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Fundição (copy)</t>
   </si>
   <si>
+    <t>8337249227</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Acabamento (copy)</t>
   </si>
   <si>
+    <t>8337249260</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Usinagem (copy)</t>
   </si>
   <si>
+    <t>8337249288</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Inspeção (copy)</t>
   </si>
   <si>
+    <t>8337147959</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Fundição</t>
   </si>
   <si>
+    <t>8337148003</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Acabamento</t>
   </si>
   <si>
+    <t>8337148049</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Usinagem</t>
   </si>
   <si>
+    <t>8337148071</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Inspeção</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>8337249374</t>
   </si>
   <si>
     <t>Gerar registro no Benner (BLOCO K)</t>
   </si>
   <si>
+    <t>8337249444</t>
+  </si>
+  <si>
     <t>Rateio tempos usinagem</t>
   </si>
   <si>
-    <t>29001</t>
+    <t>04/02/2025</t>
+  </si>
+  <si>
+    <t>8337249480</t>
   </si>
   <si>
     <t>Correção</t>
@@ -369,31 +474,31 @@
     <t>ERRO SALDO 108892/93</t>
   </si>
   <si>
-    <t>28847</t>
+    <t>8337249570</t>
   </si>
   <si>
     <t>Habilitar o sistema de apontamento dos manipuladores para o acabamento</t>
   </si>
   <si>
-    <t>29132</t>
+    <t>8337249616</t>
   </si>
   <si>
     <t>Melhorias sistema Ronda</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>8337249656</t>
   </si>
   <si>
     <t>Atualização das parcelas programadas - Reunião</t>
   </si>
   <si>
-    <t>26389</t>
+    <t>8337249735</t>
   </si>
   <si>
     <t>Controle Automático de n° sequencial de peça para ID de Bruto</t>
   </si>
   <si>
-    <t>28957</t>
+    <t>8210519804</t>
   </si>
   <si>
     <t>Controle estoque manutenção usinagem</t>
@@ -402,204 +507,225 @@
     <t>10/01/2025</t>
   </si>
   <si>
+    <t>02/02/2025</t>
+  </si>
+  <si>
+    <t>8250643367</t>
+  </si>
+  <si>
     <t>Possibilidade de subdividir eventos</t>
   </si>
   <si>
     <t>15/01/2025</t>
   </si>
   <si>
-    <t>29184</t>
+    <t>8232353294</t>
   </si>
   <si>
     <t>Ensaio de peça seriada e RX está sendo criado na etapa errada</t>
   </si>
   <si>
-    <t>29709</t>
+    <t>8327445487</t>
   </si>
   <si>
     <t>Habilitar a coluna</t>
   </si>
   <si>
-    <t>29694</t>
+    <t>8327449542</t>
   </si>
   <si>
     <t>Inserir pergunta MPO - Torno Mausa e Mandriladora Tos</t>
   </si>
   <si>
-    <t>29673</t>
+    <t>8327458188</t>
   </si>
   <si>
     <t>Itens comerciais</t>
   </si>
   <si>
-    <t>29668</t>
+    <t>8327459900</t>
   </si>
   <si>
     <t>Coluna código do cliente no relatório de comissões</t>
   </si>
   <si>
-    <t>29659</t>
+    <t>8327463054</t>
   </si>
   <si>
     <t>Melhoria relatório de comissões</t>
   </si>
   <si>
-    <t>29655</t>
+    <t>8327465911</t>
   </si>
   <si>
     <t>Aviso - financeiro em notas sem OC</t>
   </si>
   <si>
-    <t>29629</t>
+    <t>8327466994</t>
   </si>
   <si>
     <t>Inclusão de campo na planilha SPS</t>
   </si>
   <si>
-    <t>29622</t>
+    <t>08/02/2025</t>
+  </si>
+  <si>
+    <t>8327470782</t>
   </si>
   <si>
     <t>BLOQUEIO DE REQUISIÇÃO MANUAL</t>
   </si>
   <si>
-    <t>29620</t>
+    <t>8327471925</t>
   </si>
   <si>
     <t>Regras do controle de saldo do EPI</t>
   </si>
   <si>
-    <t>29569</t>
+    <t>8327483088</t>
   </si>
   <si>
     <t>Acesso ao Setor 7272</t>
   </si>
   <si>
-    <t>29551</t>
+    <t>8327484774</t>
   </si>
   <si>
     <t>Incluir texto na tela da pré-lista</t>
   </si>
   <si>
-    <t>29545</t>
+    <t>8327487987</t>
   </si>
   <si>
     <t>Ajuste Automático nos Centros de Custo</t>
   </si>
   <si>
-    <t>29544</t>
+    <t>8327489122</t>
   </si>
   <si>
     <t>Dashboard Desmoldagem USE</t>
   </si>
   <si>
-    <t>29525</t>
+    <t>8327492715</t>
   </si>
   <si>
     <t>CFOP Imobilizado</t>
   </si>
   <si>
-    <t>29524</t>
+    <t>8327493915</t>
   </si>
   <si>
     <t>Atualização de relatório NF de entrada</t>
   </si>
   <si>
-    <t>29520</t>
+    <t>8327498326</t>
   </si>
   <si>
     <t>Planilha de Recibo Embarque - Vínculo NFe X Sequência</t>
   </si>
   <si>
-    <t>29519</t>
+    <t>8327500676</t>
   </si>
   <si>
     <t>Sistema de Materiais Endereçados</t>
   </si>
   <si>
-    <t>29516</t>
+    <t>8327503406</t>
   </si>
   <si>
     <t>Abertura de conserto de modelo</t>
   </si>
   <si>
-    <t>29499</t>
+    <t>8327509219</t>
   </si>
   <si>
     <t>Tempo padrão - CPP x CRP</t>
   </si>
   <si>
-    <t>29489</t>
+    <t>8327512146</t>
   </si>
   <si>
     <t>Atualização do sistema CPC/OTF</t>
   </si>
   <si>
-    <t>29488</t>
+    <t>8327516330</t>
   </si>
   <si>
     <t>Controle na geração de Sequencias</t>
   </si>
   <si>
-    <t>29470</t>
+    <t>8327525253</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - Cálculo de Ociosidade x Custo Fixo</t>
   </si>
   <si>
-    <t>29466</t>
+    <t>8327526746</t>
   </si>
   <si>
     <t>Preenchimento automático de coleta realizada</t>
   </si>
   <si>
-    <t>28743</t>
+    <t>8327528976</t>
   </si>
   <si>
     <t>Iintegração de requisição gerado no ERP &gt; Nimbi</t>
   </si>
   <si>
+    <t>8330436373</t>
+  </si>
+  <si>
     <t>Iintegração de requisição gerado no ERP &gt; Nimbi (Análise  API)</t>
   </si>
   <si>
-    <t>29708</t>
+    <t>30/01/2025</t>
+  </si>
+  <si>
+    <t>8340721851</t>
   </si>
   <si>
     <t>Inclusão da informação de ligas - QlikSense</t>
   </si>
   <si>
-    <t>28/01/2025</t>
-  </si>
-  <si>
-    <t>29170</t>
+    <t>8337371774</t>
   </si>
   <si>
     <t>Melhorias apontamento de solda</t>
   </si>
   <si>
-    <t>29293</t>
+    <t>8337371820</t>
   </si>
   <si>
     <t>MELHORIAS APONTAMENTO MANIPULADOR PEQUENO</t>
   </si>
   <si>
-    <t>29333</t>
+    <t>8209965692</t>
   </si>
   <si>
     <t>Conferencia de nota fiscal - almoxarifado</t>
   </si>
   <si>
-    <t>29660</t>
+    <t>8340608464</t>
   </si>
   <si>
     <t>Importar status do plano de ação</t>
   </si>
   <si>
+    <t>8340622822</t>
+  </si>
+  <si>
     <t>Lembrete planos de ação a vencer</t>
   </si>
   <si>
+    <t>8340627052</t>
+  </si>
+  <si>
     <t>Inserir setas de identificação do indicador</t>
   </si>
   <si>
+    <t>8340633357</t>
+  </si>
+  <si>
     <t>Planos e ação de indicadores comerciais acompanhar calendário comercial</t>
   </si>
   <si>
@@ -609,7 +735,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-3</t>
+    <t>Mar/2022</t>
   </si>
   <si>
     <t>Base</t>
@@ -663,10 +789,16 @@
     <t>Sim</t>
   </si>
   <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
     <t>Abertos</t>
   </si>
   <si>
     <t>Impedimento</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Não definida</t>
@@ -1245,10 +1377,10 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
@@ -1262,22 +1394,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1289,27 +1421,27 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1321,10 +1453,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1336,27 +1468,27 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1368,10 +1500,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1383,27 +1515,27 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1415,10 +1547,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1430,27 +1562,27 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1462,10 +1594,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1477,27 +1609,27 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1509,10 +1641,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1524,27 +1656,27 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1556,10 +1688,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1571,42 +1703,42 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1618,42 +1750,42 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1665,42 +1797,42 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1712,42 +1844,42 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1759,42 +1891,42 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1806,42 +1938,42 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1853,42 +1985,42 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1900,42 +2032,42 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1947,42 +2079,42 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1994,42 +2126,42 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2041,42 +2173,42 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2088,42 +2220,42 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2135,45 +2267,45 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
@@ -2182,45 +2314,45 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -2229,27 +2361,27 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2261,10 +2393,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2276,27 +2408,27 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2308,10 +2440,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2323,27 +2455,27 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2355,10 +2487,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2370,27 +2502,27 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2402,10 +2534,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2417,27 +2549,27 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2449,10 +2581,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2464,27 +2596,27 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2496,13 +2628,13 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
@@ -2511,27 +2643,27 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2543,10 +2675,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2558,10 +2690,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2570,15 +2702,15 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2590,10 +2722,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2605,104 +2737,104 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="K33" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2711,33 +2843,33 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
@@ -2746,45 +2878,45 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>21</v>
@@ -2793,42 +2925,42 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2840,42 +2972,42 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2887,42 +3019,42 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2934,42 +3066,42 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2981,42 +3113,42 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3028,42 +3160,42 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3075,42 +3207,42 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3122,42 +3254,42 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3169,27 +3301,27 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3201,13 +3333,13 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>21</v>
@@ -3216,45 +3348,45 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>21</v>
@@ -3263,42 +3395,42 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3310,10 +3442,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3322,30 +3454,30 @@
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3357,27 +3489,27 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3389,10 +3521,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3404,42 +3536,42 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3451,27 +3583,27 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3483,13 +3615,13 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>21</v>
@@ -3498,27 +3630,27 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3530,10 +3662,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3545,45 +3677,45 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>21</v>
@@ -3592,27 +3724,27 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3624,10 +3756,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3639,27 +3771,27 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3671,10 +3803,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3686,27 +3818,27 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3718,10 +3850,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3733,27 +3865,27 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3765,10 +3897,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3780,27 +3912,27 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3812,10 +3944,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3827,27 +3959,27 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3859,10 +3991,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3874,27 +4006,27 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -3906,10 +4038,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -3921,27 +4053,27 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -3953,10 +4085,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -3968,27 +4100,27 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>184</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4000,10 +4132,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4015,27 +4147,27 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4047,10 +4179,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4062,27 +4194,27 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4094,10 +4226,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4109,27 +4241,27 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>184</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4141,10 +4273,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4156,27 +4288,27 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4188,10 +4320,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4203,27 +4335,27 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4235,10 +4367,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4250,27 +4382,27 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4282,10 +4414,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4297,27 +4429,27 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4329,10 +4461,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4344,27 +4476,27 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4376,10 +4508,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4391,27 +4523,27 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
@@ -4423,10 +4555,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -4438,27 +4570,27 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4470,13 +4602,13 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>21</v>
@@ -4485,27 +4617,27 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4517,10 +4649,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4532,27 +4664,27 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4564,10 +4696,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4579,27 +4711,27 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4611,10 +4743,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4626,27 +4758,27 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>184</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>175</v>
+        <v>213</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4658,13 +4790,13 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>21</v>
@@ -4673,27 +4805,27 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
@@ -4705,10 +4837,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -4720,45 +4852,45 @@
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>21</v>
@@ -4767,45 +4899,45 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>21</v>
@@ -4814,27 +4946,27 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>221</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
@@ -4846,10 +4978,10 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -4861,45 +4993,45 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>21</v>
@@ -4908,27 +5040,27 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -4940,13 +5072,13 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>21</v>
@@ -4955,27 +5087,27 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
@@ -4987,10 +5119,10 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5002,10 +5134,10 @@
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>25</v>
@@ -5014,30 +5146,30 @@
         <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5049,42 +5181,42 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5096,42 +5228,42 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5143,42 +5275,42 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>191</v>
+        <v>236</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5190,22 +5322,22 @@
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -5221,23 +5353,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="E2" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5245,16 +5377,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5265,20 +5397,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>19.53</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>205</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K22">
         <v>67</v>
@@ -5286,7 +5418,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="K23">
         <v>11</v>
@@ -5294,7 +5426,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5325,12 +5457,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="B2">
         <v>86</v>
@@ -5344,35 +5476,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>208</v>
+        <v>250</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5380,7 +5512,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -5389,48 +5521,54 @@
         <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N10">
         <v>67</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>258</v>
       </c>
       <c r="Q10">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E11">
         <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H11">
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="K11">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M11" t="s">
         <v>25</v>
@@ -5439,15 +5577,15 @@
         <v>5</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>13</v>
@@ -5459,59 +5597,65 @@
         <v>69</v>
       </c>
       <c r="J12" t="s">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q12">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N13">
         <v>3</v>
       </c>
+      <c r="P13" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="N14">
         <v>11</v>
@@ -5519,7 +5663,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5527,7 +5671,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5535,7 +5679,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>221</v>
+        <v>265</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5543,10 +5687,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5554,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5562,142 +5706,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>159</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>33</v>
+        <v>228</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>52</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>1044</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>1044</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
